--- a/mock-data/execution-master-data.xlsx
+++ b/mock-data/execution-master-data.xlsx
@@ -825,7 +825,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>DOC-SDS-CHM</t>
+          <t>DOC-SDS-FIN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -835,12 +835,12 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>SKU-CHM-9100</t>
+          <t>SKU-FIN-9100</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>sds/SKU-CHM-9100_v4.2.pdf</t>
+          <t>sds/SKU-FIN-9100_v4.2.pdf</t>
         </is>
       </c>
     </row>
